--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_La Laguna Tenerife.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2040.12</v>
+        <v>2351.8</v>
       </c>
       <c r="C2" t="n">
-        <v>2042.92</v>
+        <v>2351.06</v>
       </c>
       <c r="D2" t="n">
-        <v>121.4927652575725</v>
+        <v>121.1793829166418</v>
       </c>
       <c r="E2" t="n">
-        <v>115.6677696630314</v>
+        <v>117.2662543703691</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5859188544152745</v>
+        <v>0.5839322381930184</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1356310834530078</v>
+        <v>0.1324197397798137</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2547169811320755</v>
+        <v>0.2494929006085193</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3090692124105012</v>
+        <v>0.2946611909650924</v>
       </c>
       <c r="J2" t="n">
-        <v>253</v>
+        <v>293</v>
       </c>
       <c r="K2" t="n">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="M2" t="n">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="N2" t="n">
-        <v>815</v>
+        <v>919</v>
       </c>
       <c r="O2" t="n">
-        <v>1032</v>
+        <v>1163</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6157517899761337</v>
+        <v>0.5970225872689938</v>
       </c>
       <c r="Q2" t="n">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="R2" t="n">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1378281622911695</v>
+        <v>0.1442505133470226</v>
       </c>
       <c r="T2" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="U2" t="n">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1646778042959427</v>
+        <v>0.1688911704312115</v>
       </c>
       <c r="W2" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="X2" t="n">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1258949880668258</v>
+        <v>0.12217659137577</v>
       </c>
       <c r="Z2" t="n">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="AA2" t="n">
-        <v>549</v>
+        <v>632</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3275656324582339</v>
+        <v>0.324435318275154</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7897286821705426</v>
+        <v>0.7901977644024075</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4372294372294372</v>
+        <v>0.4341637010676156</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4746376811594203</v>
+        <v>0.4650455927051672</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4691943127962085</v>
+        <v>0.4495798319327731</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3697632058287796</v>
+        <v>0.3765822784810127</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.579457364341085</v>
+        <v>1.580395528804815</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9492753623188406</v>
+        <v>0.9300911854103343</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.192105263157895</v>
+        <v>1.189655172413793</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7574850299401198</v>
+        <v>0.7690288713910761</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.296296296296296</v>
+        <v>1.288617886178862</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.382978723404255</v>
+        <v>1.392857142857143</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.65359477124183</v>
+        <v>1.656976744186047</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.477124183006536</v>
+        <v>5.662790697674419</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.130718954248366</v>
+        <v>7.319767441860465</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.86142857142856</v>
+        <v>73.49374999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>72.96142857142857</v>
+        <v>73.47062500000001</v>
       </c>
       <c r="D3" t="n">
-        <v>121.4927652575725</v>
+        <v>121.1793829166418</v>
       </c>
       <c r="E3" t="n">
-        <v>115.6677696630313</v>
+        <v>117.2662543703691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5859188544152744</v>
+        <v>0.5839322381930184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1356310834530078</v>
+        <v>0.1324197397798137</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2547169811320755</v>
+        <v>0.2494929006085193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3090692124105012</v>
+        <v>0.2946611909650924</v>
       </c>
       <c r="J3" t="n">
-        <v>9.035714285714286</v>
+        <v>9.15625</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>9.90625</v>
       </c>
       <c r="L3" t="n">
-        <v>2.321428571428572</v>
+        <v>2.4375</v>
       </c>
       <c r="M3" t="n">
-        <v>9.928571428571429</v>
+        <v>9.8125</v>
       </c>
       <c r="N3" t="n">
-        <v>29.10714285714286</v>
+        <v>28.71875</v>
       </c>
       <c r="O3" t="n">
-        <v>36.85714285714285</v>
+        <v>36.34375</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6157517899761336</v>
+        <v>0.5970225872689938</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.607142857142857</v>
+        <v>3.8125</v>
       </c>
       <c r="R3" t="n">
-        <v>8.25</v>
+        <v>8.78125</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1378281622911695</v>
+        <v>0.1442505133470226</v>
       </c>
       <c r="T3" t="n">
-        <v>4.678571428571429</v>
+        <v>4.78125</v>
       </c>
       <c r="U3" t="n">
-        <v>9.857142857142858</v>
+        <v>10.28125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1646778042959427</v>
+        <v>0.1688911704312115</v>
       </c>
       <c r="W3" t="n">
-        <v>3.535714285714286</v>
+        <v>3.34375</v>
       </c>
       <c r="X3" t="n">
-        <v>7.535714285714286</v>
+        <v>7.4375</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1258949880668258</v>
+        <v>0.12217659137577</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.25</v>
+        <v>7.4375</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.60714285714286</v>
+        <v>19.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3275656324582339</v>
+        <v>0.324435318275154</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7897286821705427</v>
+        <v>0.7901977644024075</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4372294372294372</v>
+        <v>0.4341637010676156</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4746376811594203</v>
+        <v>0.4650455927051672</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4691943127962085</v>
+        <v>0.4495798319327731</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3697632058287796</v>
+        <v>0.3765822784810127</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.579457364341085</v>
+        <v>1.580395528804815</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9492753623188406</v>
+        <v>0.9300911854103343</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.192105263157895</v>
+        <v>1.189655172413793</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7574850299401198</v>
+        <v>0.7690288713910761</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.296296296296296</v>
+        <v>1.288617886178862</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.382978723404255</v>
+        <v>1.392857142857143</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.65359477124183</v>
+        <v>1.656976744186047</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.477124183006536</v>
+        <v>5.662790697674419</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.130718954248366</v>
+        <v>7.319767441860465</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2045.72</v>
+        <v>2350.32</v>
       </c>
       <c r="C4" t="n">
-        <v>2042.92</v>
+        <v>2351.06</v>
       </c>
       <c r="D4" t="n">
-        <v>115.6677696630314</v>
+        <v>117.2662543703691</v>
       </c>
       <c r="E4" t="n">
-        <v>121.4927652575725</v>
+        <v>121.1793829166418</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5488088320743754</v>
+        <v>0.5632008154943935</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1436732165594136</v>
+        <v>0.1436478253001146</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3076074972436604</v>
+        <v>0.2969518190757129</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2754212667054038</v>
+        <v>0.2787971457696228</v>
       </c>
       <c r="J4" t="n">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="L4" t="n">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="M4" t="n">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="N4" t="n">
-        <v>839</v>
+        <v>972</v>
       </c>
       <c r="O4" t="n">
-        <v>1119</v>
+        <v>1278</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6502033701336433</v>
+        <v>0.6513761467889908</v>
       </c>
       <c r="Q4" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="R4" t="n">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1824520627542127</v>
+        <v>0.1778797145769623</v>
       </c>
       <c r="T4" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="U4" t="n">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="V4" t="n">
-        <v>0.136548518303312</v>
+        <v>0.1452599388379205</v>
       </c>
       <c r="W4" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="X4" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08890180127832656</v>
+        <v>0.08664627930682976</v>
       </c>
       <c r="Z4" t="n">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="AA4" t="n">
-        <v>513</v>
+        <v>583</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2980825101685067</v>
+        <v>0.2971457696228338</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7497765862377123</v>
+        <v>0.7605633802816901</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3949044585987261</v>
+        <v>0.4068767908309456</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4</v>
+        <v>0.3929824561403509</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4640522875816994</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3313840155945419</v>
+        <v>0.3499142367066895</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.499553172475425</v>
+        <v>1.52112676056338</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.8</v>
+        <v>0.7859649122807018</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.085585585585586</v>
+        <v>1.131474103585657</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.058823529411765</v>
+        <v>1.034883720930233</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.974910394265233</v>
+        <v>1.026490066225165</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.821428571428571</v>
+        <v>1.780952380952381</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.335329341317365</v>
+        <v>1.328083989501312</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.152694610778443</v>
+        <v>5.149606299212598</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.488023952095809</v>
+        <v>6.477690288713911</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.06142857142856</v>
+        <v>73.44750000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>72.96142857142857</v>
+        <v>73.47062500000001</v>
       </c>
       <c r="D5" t="n">
-        <v>115.6677696630313</v>
+        <v>117.2662543703691</v>
       </c>
       <c r="E5" t="n">
-        <v>121.4927652575725</v>
+        <v>121.1793829166418</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5488088320743755</v>
+        <v>0.5632008154943935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1436732165594136</v>
+        <v>0.1436478253001146</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3076074972436604</v>
+        <v>0.2969518190757129</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2754212667054038</v>
+        <v>0.2787971457696228</v>
       </c>
       <c r="J5" t="n">
-        <v>11.57142857142857</v>
+        <v>11.125</v>
       </c>
       <c r="K5" t="n">
-        <v>9.714285714285714</v>
+        <v>9.6875</v>
       </c>
       <c r="L5" t="n">
-        <v>5.464285714285714</v>
+        <v>5.84375</v>
       </c>
       <c r="M5" t="n">
-        <v>10.92857142857143</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>29.96428571428572</v>
+        <v>30.375</v>
       </c>
       <c r="O5" t="n">
-        <v>39.96428571428572</v>
+        <v>39.9375</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6502033701336433</v>
+        <v>0.6513761467889908</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.428571428571429</v>
+        <v>4.4375</v>
       </c>
       <c r="R5" t="n">
-        <v>11.21428571428571</v>
+        <v>10.90625</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1824520627542127</v>
+        <v>0.1778797145769623</v>
       </c>
       <c r="T5" t="n">
-        <v>3.357142857142857</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>8.392857142857142</v>
+        <v>8.90625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.136548518303312</v>
+        <v>0.1452599388379205</v>
       </c>
       <c r="W5" t="n">
-        <v>2.535714285714286</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.464285714285714</v>
+        <v>5.3125</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08890180127832656</v>
+        <v>0.08664627930682976</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.071428571428571</v>
+        <v>6.375</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.32142857142857</v>
+        <v>18.21875</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2980825101685067</v>
+        <v>0.2971457696228338</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7497765862377123</v>
+        <v>0.7605633802816901</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3949044585987261</v>
+        <v>0.4068767908309456</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4</v>
+        <v>0.3929824561403509</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4640522875816993</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3313840155945419</v>
+        <v>0.3499142367066895</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.499553172475425</v>
+        <v>1.52112676056338</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.8</v>
+        <v>0.7859649122807018</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.085585585585586</v>
+        <v>1.131474103585657</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.058823529411765</v>
+        <v>1.034883720930233</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.974910394265233</v>
+        <v>1.026490066225165</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.821428571428571</v>
+        <v>1.780952380952381</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.335329341317365</v>
+        <v>1.328083989501312</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.152694610778443</v>
+        <v>5.149606299212598</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.488023952095808</v>
+        <v>6.477690288713911</v>
       </c>
     </row>
     <row r="7">
@@ -1559,13 +1559,13 @@
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AY8" t="n">
         <v>0.001</v>
@@ -1578,67 +1578,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H9" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I9" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J9" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K9" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>36</v>
+      </c>
+      <c r="R9" t="n">
+        <v>57</v>
+      </c>
+      <c r="S9" t="n">
+        <v>97</v>
+      </c>
+      <c r="T9" t="n">
+        <v>347</v>
+      </c>
+      <c r="U9" t="n">
+        <v>56</v>
+      </c>
+      <c r="V9" t="n">
         <v>32</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>32</v>
-      </c>
-      <c r="R9" t="n">
-        <v>52</v>
-      </c>
-      <c r="S9" t="n">
-        <v>92</v>
-      </c>
-      <c r="T9" t="n">
-        <v>326</v>
-      </c>
-      <c r="U9" t="n">
-        <v>51</v>
-      </c>
-      <c r="V9" t="n">
-        <v>30</v>
       </c>
       <c r="W9" t="n">
         <v>5</v>
@@ -1647,31 +1647,31 @@
         <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="Z9" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.703</v>
+        <v>0.694</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.464</v>
+        <v>0.389</v>
       </c>
       <c r="AE9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.361</v>
+        <v>0.378</v>
       </c>
       <c r="AH9" t="n">
         <v>3</v>
@@ -1683,51 +1683,51 @@
         <v>0.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AL9" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.395</v>
+        <v>0.398</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>502:45</t>
+          <t>551:53</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>282.4</v>
+        <v>309.72</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.523</v>
+        <v>0.515</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.573</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.016</v>
+        <v>0.994</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.113</v>
+        <v>0.116</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.3</v>
+        <v>0.281</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.312</v>
+        <v>2.306</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.279</v>
+        <v>0.278</v>
       </c>
       <c r="AW9" t="n">
         <v>0.026</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="10">
@@ -1737,67 +1737,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
+        <v>43</v>
+      </c>
+      <c r="G10" t="n">
+        <v>83</v>
+      </c>
+      <c r="H10" t="n">
         <v>38</v>
       </c>
-      <c r="G10" t="n">
-        <v>68</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
+        <v>44</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18</v>
+      </c>
+      <c r="K10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>23</v>
+      </c>
+      <c r="R10" t="n">
+        <v>44</v>
+      </c>
+      <c r="S10" t="n">
         <v>34</v>
       </c>
-      <c r="I10" t="n">
-        <v>38</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>11</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>22</v>
-      </c>
-      <c r="R10" t="n">
-        <v>39</v>
-      </c>
-      <c r="S10" t="n">
-        <v>31</v>
-      </c>
       <c r="T10" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="U10" t="n">
         <v>14</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
@@ -1806,87 +1806,87 @@
         <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Z10" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.891</v>
+        <v>0.87</v>
       </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
         <v>0.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.611</v>
+        <v>0.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.54</v>
+        <v>0.525</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>258:52</t>
+          <t>311:42</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>128.72</v>
+        <v>155.36</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.744</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.787</v>
+        <v>0.729</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.305</v>
+        <v>1.242</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.171</v>
+        <v>0.148</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.378</v>
+        <v>0.336</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.783</v>
       </c>
       <c r="AV10" t="n">
         <v>0.247</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="11">
@@ -1896,40 +1896,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="H11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J11" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N11" t="n">
         <v>9</v>
@@ -1938,19 +1938,19 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R11" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="S11" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="T11" t="n">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="U11" t="n">
         <v>14</v>
@@ -1959,93 +1959,93 @@
         <v>24</v>
       </c>
       <c r="W11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Z11" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.85</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.333</v>
+        <v>0.438</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.636</v>
+        <v>0.667</v>
       </c>
       <c r="AH11" t="n">
         <v>6</v>
       </c>
       <c r="AI11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.429</v>
+        <v>0.353</v>
       </c>
       <c r="AK11" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="AL11" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.324</v>
+        <v>0.339</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>581:01</t>
+          <t>674:37</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>213.12</v>
+        <v>252.2</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.506</v>
+        <v>0.519</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.57</v>
+        <v>0.573</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.953</v>
+        <v>0.964</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.164</v>
+        <v>0.159</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.28</v>
+        <v>0.255</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.029</v>
+        <v>2.225</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.182</v>
+        <v>0.185</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.092</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -2214,67 +2214,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E13" t="n">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H13" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I13" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J13" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="K13" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="Q13" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="R13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S13" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="T13" t="n">
-        <v>466</v>
+        <v>514</v>
       </c>
       <c r="U13" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="V13" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="W13" t="n">
         <v>13</v>
@@ -2283,31 +2283,31 @@
         <v>9</v>
       </c>
       <c r="Y13" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Z13" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AA13" t="n">
         <v>0.826</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AC13" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AD13" t="n">
         <v>0.431</v>
       </c>
       <c r="AE13" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AF13" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="AH13" t="n">
         <v>3</v>
@@ -2319,51 +2319,51 @@
         <v>0.6</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.381</v>
+        <v>0.397</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>613:15</t>
+          <t>658:19</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>402.88</v>
+        <v>448.96</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.548</v>
+        <v>0.546</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="AR13" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.238</v>
+        <v>0.234</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.209</v>
+        <v>2.133</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.326</v>
+        <v>0.337</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.218</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="14">
@@ -2373,67 +2373,67 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>32</v>
+      </c>
+      <c r="C14" t="n">
+        <v>202</v>
+      </c>
+      <c r="D14" t="n">
+        <v>54</v>
+      </c>
+      <c r="E14" t="n">
+        <v>81</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>58</v>
+      </c>
+      <c r="H14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I14" t="n">
+        <v>48</v>
+      </c>
+      <c r="J14" t="n">
         <v>28</v>
       </c>
-      <c r="C14" t="n">
-        <v>183</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="K14" t="n">
+        <v>74</v>
+      </c>
+      <c r="L14" t="n">
+        <v>34</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>10</v>
+      </c>
+      <c r="R14" t="n">
         <v>48</v>
       </c>
-      <c r="E14" t="n">
-        <v>74</v>
-      </c>
-      <c r="F14" t="n">
-        <v>16</v>
-      </c>
-      <c r="G14" t="n">
-        <v>52</v>
-      </c>
-      <c r="H14" t="n">
-        <v>39</v>
-      </c>
-      <c r="I14" t="n">
-        <v>47</v>
-      </c>
-      <c r="J14" t="n">
-        <v>26</v>
-      </c>
-      <c r="K14" t="n">
-        <v>61</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="S14" t="n">
+        <v>45</v>
+      </c>
+      <c r="T14" t="n">
+        <v>279</v>
+      </c>
+      <c r="U14" t="n">
+        <v>30</v>
+      </c>
+      <c r="V14" t="n">
         <v>33</v>
-      </c>
-      <c r="M14" t="n">
-        <v>16</v>
-      </c>
-      <c r="N14" t="n">
-        <v>8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>41</v>
-      </c>
-      <c r="T14" t="n">
-        <v>247</v>
-      </c>
-      <c r="U14" t="n">
-        <v>28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>31</v>
       </c>
       <c r="W14" t="n">
         <v>4</v>
@@ -2442,22 +2442,22 @@
         <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Z14" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.819</v>
+        <v>0.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2469,60 +2469,60 @@
         <v>0.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI14" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.429</v>
+        <v>0.419</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.167</v>
+        <v>0.185</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>509:22</t>
+          <t>605:04</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>154.68</v>
+        <v>170.12</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.571</v>
+        <v>0.583</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.624</v>
+        <v>0.631</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.183</v>
+        <v>1.187</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.31</v>
+        <v>0.288</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.151</v>
+        <v>0.139</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.148</v>
+        <v>0.155</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="15">
@@ -2691,22 +2691,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
@@ -2718,10 +2718,10 @@
         <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
         <v>14</v>
@@ -2739,13 +2739,13 @@
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U16" t="n">
         <v>6</v>
@@ -2772,10 +2772,10 @@
         <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2796,51 +2796,51 @@
         <v>0.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.4</v>
+        <v>0.409</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>298:05</t>
+          <t>342:20</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>55.52</v>
+        <v>58.52</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.532</v>
+        <v>0.53</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.554</v>
+        <v>0.551</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.009</v>
+        <v>1.008</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.128</v>
+        <v>0.12</v>
       </c>
       <c r="AU16" t="n">
         <v>4.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AW16" t="n">
         <v>0.027</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="17">
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2928,60 +2928,60 @@
         <v>1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
         <v>2</v>
       </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1</v>
-      </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AS17" t="n">
         <v>0.2</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.286</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
@@ -2990,7 +2990,7 @@
         <v>0.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.198</v>
+        <v>0.241</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>359</v>
+        <v>398</v>
       </c>
       <c r="D18" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E18" t="n">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -3027,22 +3027,22 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="I18" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="L18" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
         <v>23</v>
@@ -3051,58 +3051,58 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R18" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="T18" t="n">
-        <v>501</v>
+        <v>555</v>
       </c>
       <c r="U18" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="V18" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="W18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="n">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="Z18" t="n">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.826</v>
+        <v>0.828</v>
       </c>
       <c r="AB18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.5</v>
+        <v>0.473</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -3124,41 +3124,41 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>575:44</t>
+          <t>653:46</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>262</v>
+        <v>289.84</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.715</v>
+        <v>0.706</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.767</v>
+        <v>0.763</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.37</v>
+        <v>1.373</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.575</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.893</v>
+        <v>0.966</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.226</v>
+        <v>0.219</v>
       </c>
       <c r="AW18" t="n">
         <v>0.08</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.204</v>
+        <v>0.207</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="19">
@@ -3168,156 +3168,156 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>32</v>
+      </c>
+      <c r="C19" t="n">
+        <v>186</v>
+      </c>
+      <c r="D19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E19" t="n">
+        <v>53</v>
+      </c>
+      <c r="F19" t="n">
         <v>28</v>
       </c>
-      <c r="C19" t="n">
-        <v>139</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17</v>
-      </c>
-      <c r="E19" t="n">
-        <v>37</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
+        <v>75</v>
+      </c>
+      <c r="H19" t="n">
+        <v>42</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" t="n">
+        <v>74</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>11</v>
+      </c>
+      <c r="R19" t="n">
+        <v>61</v>
+      </c>
+      <c r="S19" t="n">
+        <v>47</v>
+      </c>
+      <c r="T19" t="n">
+        <v>226</v>
+      </c>
+      <c r="U19" t="n">
+        <v>19</v>
+      </c>
+      <c r="V19" t="n">
         <v>24</v>
       </c>
-      <c r="G19" t="n">
-        <v>64</v>
-      </c>
-      <c r="H19" t="n">
-        <v>33</v>
-      </c>
-      <c r="I19" t="n">
-        <v>40</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="W19" t="n">
+        <v>8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>76</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC19" t="n">
         <v>18</v>
       </c>
-      <c r="K19" t="n">
-        <v>62</v>
-      </c>
-      <c r="L19" t="n">
-        <v>14</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="AD19" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AH19" t="n">
         <v>13</v>
       </c>
-      <c r="N19" t="n">
-        <v>10</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>51</v>
-      </c>
-      <c r="S19" t="n">
-        <v>40</v>
-      </c>
-      <c r="T19" t="n">
-        <v>169</v>
-      </c>
-      <c r="U19" t="n">
-        <v>11</v>
-      </c>
-      <c r="V19" t="n">
-        <v>22</v>
-      </c>
-      <c r="W19" t="n">
-        <v>4</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>12</v>
-      </c>
       <c r="AI19" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.429</v>
+        <v>0.419</v>
       </c>
       <c r="AK19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AL19" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.333</v>
+        <v>0.341</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>466:39</t>
+          <t>558:12</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>127.6</v>
+        <v>161</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.525</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.586</v>
+        <v>0.62</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.089</v>
+        <v>1.155</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="AU19" t="n">
-        <v>2</v>
+        <v>1.818</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.136</v>
+        <v>0.143</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.04</v>
+        <v>0.047</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.164</v>
+        <v>0.168</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="20">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>2</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.292</v>
+        <v>0.291</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>29</v>
+      </c>
+      <c r="C21" t="n">
+        <v>207</v>
+      </c>
+      <c r="D21" t="n">
         <v>28</v>
       </c>
-      <c r="C21" t="n">
-        <v>198</v>
-      </c>
-      <c r="D21" t="n">
-        <v>27</v>
-      </c>
       <c r="E21" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H21" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J21" t="n">
         <v>14</v>
@@ -3516,31 +3516,31 @@
         <v>61</v>
       </c>
       <c r="L21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S21" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T21" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="U21" t="n">
         <v>26</v>
@@ -3555,22 +3555,22 @@
         <v>7</v>
       </c>
       <c r="Y21" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Z21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.833</v>
+        <v>0.838</v>
       </c>
       <c r="AB21" t="n">
         <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
@@ -3582,60 +3582,60 @@
         <v>0.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.474</v>
+        <v>0.488</v>
       </c>
       <c r="AK21" t="n">
         <v>16</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.333</v>
+        <v>0.327</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>510:52</t>
+          <t>524:26</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>170.92</v>
+        <v>178.36</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.631</v>
+        <v>0.634</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.158</v>
+        <v>1.161</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.304</v>
+        <v>0.299</v>
       </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.166</v>
+        <v>0.168</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="AX21" t="n">
         <v>0.147</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="22">
@@ -3645,40 +3645,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="n">
         <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3693,13 +3693,13 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -3723,10 +3723,10 @@
         <v>1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -3741,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ22" t="n">
         <v>0.5</v>
@@ -3753,45 +3753,45 @@
         <v>1</v>
       </c>
       <c r="AL22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>67:45</t>
+          <t>108:14</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.714</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.714</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AR22" t="n">
         <v>1.25</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.078</v>
+        <v>0.06</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.073</v>
+        <v>0.128</v>
       </c>
       <c r="AY22" t="n">
         <v>0.005</v>
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C23" t="n">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -3822,22 +3822,22 @@
         <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I23" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J23" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K23" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L23" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N23" t="n">
         <v>13</v>
@@ -3846,25 +3846,25 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="R23" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="S23" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="T23" t="n">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="U23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W23" t="n">
         <v>6</v>
@@ -3873,31 +3873,31 @@
         <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="Z23" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="AB23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AC23" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.452</v>
+        <v>0.447</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.4</v>
+        <v>0.286</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3919,41 +3919,41 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>459:32</t>
+          <t>529:08</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>171.8</v>
+        <v>201.64</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.603</v>
+        <v>0.607</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.635</v>
+        <v>0.637</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.019</v>
+        <v>1.022</v>
       </c>
       <c r="AS23" t="n">
         <v>0.198</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.43</v>
+        <v>0.421</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.471</v>
+        <v>1.35</v>
       </c>
       <c r="AV23" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AX23" t="n">
         <v>0.186</v>
       </c>
-      <c r="AW23" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0.185</v>
-      </c>
       <c r="AY23" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="24">
@@ -3963,22 +3963,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
         <v>53</v>
       </c>
       <c r="G24" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H24" t="n">
         <v>17</v>
@@ -3987,16 +3987,16 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
+        <v>32</v>
+      </c>
+      <c r="K24" t="n">
+        <v>79</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18</v>
+      </c>
+      <c r="M24" t="n">
         <v>29</v>
-      </c>
-      <c r="K24" t="n">
-        <v>70</v>
-      </c>
-      <c r="L24" t="n">
-        <v>17</v>
-      </c>
-      <c r="M24" t="n">
-        <v>25</v>
       </c>
       <c r="N24" t="n">
         <v>5</v>
@@ -4011,13 +4011,13 @@
         <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S24" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="T24" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="U24" t="n">
         <v>17</v>
@@ -4041,78 +4041,78 @@
         <v>0.767</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.556</v>
+        <v>0.636</v>
       </c>
       <c r="AH24" t="n">
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.532</v>
+        <v>0.51</v>
       </c>
       <c r="AK24" t="n">
         <v>28</v>
       </c>
       <c r="AL24" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.364</v>
+        <v>0.354</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>643:42</t>
+          <t>688:22</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>165.12</v>
+        <v>172.12</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.642</v>
+        <v>0.632</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.655</v>
+        <v>0.645</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.199</v>
+        <v>1.185</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.121</v>
+        <v>0.115</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.071</v>
+        <v>2.286</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.127</v>
+        <v>0.124</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.134</v>
+        <v>0.145</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="25">
@@ -4122,40 +4122,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C25" t="n">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="D25" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" t="n">
+        <v>45</v>
+      </c>
+      <c r="F25" t="n">
+        <v>33</v>
+      </c>
+      <c r="G25" t="n">
+        <v>70</v>
+      </c>
+      <c r="H25" t="n">
+        <v>27</v>
+      </c>
+      <c r="I25" t="n">
+        <v>33</v>
+      </c>
+      <c r="J25" t="n">
+        <v>15</v>
+      </c>
+      <c r="K25" t="n">
         <v>9</v>
       </c>
-      <c r="E25" t="n">
-        <v>18</v>
-      </c>
-      <c r="F25" t="n">
-        <v>19</v>
-      </c>
-      <c r="G25" t="n">
-        <v>40</v>
-      </c>
-      <c r="H25" t="n">
-        <v>17</v>
-      </c>
-      <c r="I25" t="n">
-        <v>18</v>
-      </c>
-      <c r="J25" t="n">
-        <v>8</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
@@ -4164,114 +4164,114 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>12</v>
+      </c>
+      <c r="R25" t="n">
+        <v>14</v>
+      </c>
+      <c r="S25" t="n">
+        <v>37</v>
+      </c>
+      <c r="T25" t="n">
+        <v>147</v>
+      </c>
+      <c r="U25" t="n">
+        <v>17</v>
+      </c>
+      <c r="V25" t="n">
+        <v>17</v>
+      </c>
+      <c r="W25" t="n">
+        <v>14</v>
+      </c>
+      <c r="X25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH25" t="n">
         <v>6</v>
       </c>
-      <c r="Q25" t="n">
-        <v>6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>10</v>
-      </c>
-      <c r="S25" t="n">
-        <v>17</v>
-      </c>
-      <c r="T25" t="n">
-        <v>82</v>
-      </c>
-      <c r="U25" t="n">
-        <v>4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>11</v>
-      </c>
-      <c r="X25" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>4</v>
-      </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="AK25" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AL25" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.469</v>
+        <v>0.474</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>96:17</t>
+          <t>201:50</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>71.92</v>
+        <v>141.52</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.647</v>
+        <v>0.613</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.698</v>
+        <v>0.649</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.279</v>
+        <v>1.187</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.083</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.293</v>
+        <v>0.235</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.333</v>
+        <v>1.25</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.371</v>
+        <v>0.347</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.064</v>
+        <v>0.056</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="26">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L26" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4436,157 +4436,157 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2849</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1078</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="T27" t="n">
-        <v>33</v>
+        <v>3335</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>919</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.434</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>28</v>
+        <v>2597.8</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.097</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.657</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4595,157 +4595,157 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>2482</v>
+        <v>2757</v>
       </c>
       <c r="D28" t="n">
-        <v>529</v>
+        <v>679</v>
       </c>
       <c r="E28" t="n">
-        <v>916</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="n">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="G28" t="n">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="H28" t="n">
-        <v>518</v>
+        <v>547</v>
       </c>
       <c r="I28" t="n">
-        <v>623</v>
+        <v>703</v>
       </c>
       <c r="J28" t="n">
         <v>506</v>
       </c>
       <c r="K28" t="n">
-        <v>628</v>
+        <v>740</v>
       </c>
       <c r="L28" t="n">
-        <v>216</v>
+        <v>302</v>
       </c>
       <c r="M28" t="n">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="N28" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>306</v>
+        <v>381</v>
       </c>
       <c r="Q28" t="n">
-        <v>278</v>
+        <v>352</v>
       </c>
       <c r="R28" t="n">
-        <v>588</v>
+        <v>737</v>
       </c>
       <c r="S28" t="n">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="T28" t="n">
-        <v>2936</v>
+        <v>3033</v>
       </c>
       <c r="U28" t="n">
-        <v>253</v>
+        <v>356</v>
       </c>
       <c r="V28" t="n">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="W28" t="n">
-        <v>65</v>
+        <v>187</v>
       </c>
       <c r="X28" t="n">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="Y28" t="n">
-        <v>815</v>
+        <v>972</v>
       </c>
       <c r="Z28" t="n">
-        <v>1032</v>
+        <v>1278</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.79</v>
+        <v>0.761</v>
       </c>
       <c r="AB28" t="n">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="AC28" t="n">
-        <v>231</v>
+        <v>349</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.437</v>
+        <v>0.407</v>
       </c>
       <c r="AE28" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AF28" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.475</v>
+        <v>0.393</v>
       </c>
       <c r="AH28" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="n">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="AK28" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AL28" t="n">
-        <v>549</v>
+        <v>583</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2256.12</v>
+        <v>2652.32</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.586</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.636</v>
+        <v>0.607</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.1</v>
+        <v>1.039</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.136</v>
+        <v>0.144</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.309</v>
+        <v>0.279</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.654</v>
+        <v>1.328</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.051</v>
+        <v>0.059</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.138</v>
+        <v>0.15</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4754,1400 +4754,1400 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2363</v>
-      </c>
-      <c r="D29" t="n">
-        <v>583</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1055</v>
-      </c>
-      <c r="F29" t="n">
-        <v>241</v>
-      </c>
-      <c r="G29" t="n">
-        <v>666</v>
-      </c>
-      <c r="H29" t="n">
-        <v>474</v>
-      </c>
-      <c r="I29" t="n">
-        <v>613</v>
-      </c>
-      <c r="J29" t="n">
-        <v>446</v>
-      </c>
-      <c r="K29" t="n">
-        <v>632</v>
-      </c>
-      <c r="L29" t="n">
-        <v>279</v>
-      </c>
-      <c r="M29" t="n">
-        <v>179</v>
-      </c>
-      <c r="N29" t="n">
-        <v>129</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>334</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>306</v>
-      </c>
-      <c r="R29" t="n">
-        <v>657</v>
-      </c>
-      <c r="S29" t="n">
-        <v>581</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2582</v>
-      </c>
-      <c r="U29" t="n">
-        <v>324</v>
-      </c>
-      <c r="V29" t="n">
-        <v>272</v>
-      </c>
-      <c r="W29" t="n">
-        <v>153</v>
-      </c>
-      <c r="X29" t="n">
-        <v>84</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>839</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1119</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>124</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>314</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>94</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>235</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>71</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>153</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>513</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>5600:00</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>2324.72</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.335</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
+          <t>#2 K. KOSTADINOV (Per Game)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.004</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#2 K. KOSTADINOV (Per Game)</t>
+          <t>#3 J. FERNÁNDEZ (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.778</v>
+        <v>10.267</v>
       </c>
       <c r="D31" t="n">
-        <v>0.333</v>
+        <v>2.133</v>
       </c>
       <c r="E31" t="n">
-        <v>0.444</v>
+        <v>4.4</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3.433</v>
       </c>
       <c r="H31" t="n">
-        <v>0.111</v>
+        <v>2.2</v>
       </c>
       <c r="I31" t="n">
-        <v>0.111</v>
+        <v>2.933</v>
       </c>
       <c r="J31" t="n">
-        <v>0.111</v>
+        <v>2.767</v>
       </c>
       <c r="K31" t="n">
-        <v>0.111</v>
+        <v>1.7</v>
       </c>
       <c r="L31" t="n">
-        <v>0.111</v>
+        <v>0.367</v>
       </c>
       <c r="M31" t="n">
-        <v>0.111</v>
+        <v>1.033</v>
       </c>
       <c r="N31" t="n">
-        <v>0.111</v>
+        <v>0.467</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.111</v>
+        <v>1.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.111</v>
+        <v>1.2</v>
       </c>
       <c r="R31" t="n">
-        <v>0.667</v>
+        <v>1.9</v>
       </c>
       <c r="S31" t="n">
-        <v>0.111</v>
+        <v>3.233</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>347</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.867</v>
       </c>
       <c r="V31" t="n">
-        <v>0.556</v>
+        <v>1.067</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.333</v>
+        <v>3.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.444</v>
+        <v>4.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.75</v>
+        <v>0.694</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.111</v>
+        <v>0.467</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.111</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>0.389</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.233</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.933</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>0.398</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>0.604</v>
+        <v>10.324</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.75</v>
+        <v>0.515</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.788</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.287</v>
+        <v>0.994</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.184</v>
+        <v>0.116</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.25</v>
+        <v>0.281</v>
       </c>
       <c r="AU31" t="n">
-        <v>1</v>
+        <v>2.306</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.18</v>
+        <v>0.278</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.082</v>
+        <v>0.117</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.004</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#3 J. FERNÁNDEZ (Per Game)</t>
+          <t>#4 W. VAN BECK (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C32" t="n">
-        <v>10.63</v>
+        <v>8.042</v>
       </c>
       <c r="D32" t="n">
-        <v>2.185</v>
+        <v>0.542</v>
       </c>
       <c r="E32" t="n">
-        <v>4.333</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>1.296</v>
+        <v>1.792</v>
       </c>
       <c r="G32" t="n">
-        <v>3.556</v>
+        <v>3.458</v>
       </c>
       <c r="H32" t="n">
-        <v>2.37</v>
+        <v>1.583</v>
       </c>
       <c r="I32" t="n">
-        <v>3.148</v>
+        <v>1.833</v>
       </c>
       <c r="J32" t="n">
-        <v>2.741</v>
+        <v>0.75</v>
       </c>
       <c r="K32" t="n">
-        <v>1.704</v>
+        <v>0.583</v>
       </c>
       <c r="L32" t="n">
-        <v>0.37</v>
+        <v>0.167</v>
       </c>
       <c r="M32" t="n">
-        <v>1.074</v>
+        <v>0.292</v>
       </c>
       <c r="N32" t="n">
-        <v>0.444</v>
+        <v>0.208</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.185</v>
+        <v>0.958</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.185</v>
+        <v>0.958</v>
       </c>
       <c r="R32" t="n">
-        <v>1.926</v>
+        <v>1.833</v>
       </c>
       <c r="S32" t="n">
-        <v>3.407</v>
+        <v>1.417</v>
       </c>
       <c r="T32" t="n">
-        <v>326</v>
+        <v>145</v>
       </c>
       <c r="U32" t="n">
-        <v>1.889</v>
+        <v>0.583</v>
       </c>
       <c r="V32" t="n">
-        <v>1.111</v>
+        <v>0.75</v>
       </c>
       <c r="W32" t="n">
-        <v>0.185</v>
+        <v>0.083</v>
       </c>
       <c r="X32" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.958</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.458</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
+        <v>6.473</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="AS32" t="n">
         <v>0.148</v>
       </c>
-      <c r="Y32" t="n">
-        <v>3.593</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5.111</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.037</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.185</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>10.459</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0.113</v>
-      </c>
       <c r="AT32" t="n">
-        <v>0.3</v>
+        <v>0.336</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.313</v>
+        <v>0.783</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.279</v>
+        <v>0.247</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.113</v>
+        <v>0.057</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.105</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#4 W. VAN BECK (Per Game)</t>
+          <t>#6 B. FITIPALDO (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>7.594</v>
       </c>
       <c r="D33" t="n">
-        <v>0.476</v>
+        <v>0.75</v>
       </c>
       <c r="E33" t="n">
-        <v>1.048</v>
+        <v>1.375</v>
       </c>
       <c r="F33" t="n">
-        <v>1.81</v>
+        <v>1.531</v>
       </c>
       <c r="G33" t="n">
-        <v>3.238</v>
+        <v>4.5</v>
       </c>
       <c r="H33" t="n">
-        <v>1.619</v>
+        <v>1.5</v>
       </c>
       <c r="I33" t="n">
-        <v>1.81</v>
+        <v>1.719</v>
       </c>
       <c r="J33" t="n">
-        <v>0.714</v>
+        <v>2.781</v>
       </c>
       <c r="K33" t="n">
-        <v>0.524</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>0.143</v>
+        <v>0.219</v>
       </c>
       <c r="M33" t="n">
-        <v>0.286</v>
+        <v>0.438</v>
       </c>
       <c r="N33" t="n">
-        <v>0.19</v>
+        <v>0.281</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.048</v>
+        <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.048</v>
+        <v>1.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.857</v>
+        <v>2.594</v>
       </c>
       <c r="S33" t="n">
-        <v>1.476</v>
+        <v>2.156</v>
       </c>
       <c r="T33" t="n">
-        <v>131</v>
+        <v>216</v>
       </c>
       <c r="U33" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.667</v>
       </c>
-      <c r="V33" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.952</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.2</v>
-      </c>
       <c r="AH33" t="n">
-        <v>0.524</v>
+        <v>0.188</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.857</v>
+        <v>0.531</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.611</v>
+        <v>0.353</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.286</v>
+        <v>1.344</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.381</v>
+        <v>3.969</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.54</v>
+        <v>0.339</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.13</v>
+        <v>7.881</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.744</v>
+        <v>0.519</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.787</v>
+        <v>0.573</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.305</v>
+        <v>0.964</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.171</v>
+        <v>0.159</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.378</v>
+        <v>0.255</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.6820000000000001</v>
+        <v>2.225</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.247</v>
+        <v>0.185</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.026</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#6 B. FITIPALDO (Per Game)</t>
+          <t>#7 X. LÓPEZ (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1.464</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>4.357</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.571</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1.714</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2.536</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.929</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.571</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.143</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.821</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.143</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.393</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.636</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.857</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.324</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>7.611</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.506</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.953</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.164</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.029</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#7 X. LÓPEZ (Per Game)</t>
+          <t>#9 M. HUERTAS (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>15.964</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>4.964</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>9.429</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.071</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2.607</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2.821</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>5.714</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1.964</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.821</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.679</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.679</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.893</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.464</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.464</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.464</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>3.571</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.321</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>0.826</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>0.893</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.071</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.431</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>3.321</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>6.036</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>0.964</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.429</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>16.034</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.546</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.598</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>0.996</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>0.234</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.133</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#9 M. HUERTAS (Per Game)</t>
+          <t>#11 T. SCRUBB (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>16.12</v>
+        <v>6.312</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>1.688</v>
       </c>
       <c r="E36" t="n">
-        <v>9.359999999999999</v>
+        <v>2.531</v>
       </c>
       <c r="F36" t="n">
-        <v>1.08</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>2.72</v>
+        <v>1.812</v>
       </c>
       <c r="H36" t="n">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="I36" t="n">
-        <v>3.08</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
-        <v>5.92</v>
+        <v>0.875</v>
       </c>
       <c r="K36" t="n">
-        <v>2.08</v>
+        <v>2.312</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6</v>
+        <v>1.062</v>
       </c>
       <c r="M36" t="n">
-        <v>0.52</v>
+        <v>0.625</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8</v>
+        <v>0.281</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.68</v>
+        <v>0.312</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.68</v>
+        <v>0.312</v>
       </c>
       <c r="R36" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>3.56</v>
+        <v>1.406</v>
       </c>
       <c r="T36" t="n">
-        <v>466</v>
+        <v>279</v>
       </c>
       <c r="U36" t="n">
-        <v>1.48</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.031</v>
       </c>
       <c r="W36" t="n">
-        <v>0.52</v>
+        <v>0.125</v>
       </c>
       <c r="X36" t="n">
-        <v>0.36</v>
+        <v>0.094</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.6</v>
+        <v>2.281</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.36</v>
+        <v>2.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.826</v>
+        <v>0.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.88</v>
+        <v>0.469</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.04</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.431</v>
+        <v>0.577</v>
       </c>
       <c r="AE36" t="n">
-        <v>3.4</v>
+        <v>0.188</v>
       </c>
       <c r="AF36" t="n">
-        <v>6.04</v>
+        <v>0.469</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.12</v>
+        <v>0.406</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.2</v>
+        <v>0.969</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.6</v>
+        <v>0.419</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.96</v>
+        <v>0.156</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.52</v>
+        <v>0.844</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.381</v>
+        <v>0.185</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>24:31</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>16.115</v>
+        <v>5.316</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.548</v>
+        <v>0.583</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.6</v>
+        <v>0.631</v>
       </c>
       <c r="AR36" t="n">
-        <v>1</v>
+        <v>1.187</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.166</v>
+        <v>0.059</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.238</v>
+        <v>0.288</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.209</v>
+        <v>2.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.326</v>
+        <v>0.139</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.032</v>
+        <v>0.073</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.105</v>
+        <v>0.155</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.251</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#11 T. SCRUBB (Per Game)</t>
+          <t>#13 L. COSTA (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>6.536</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1.714</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2.643</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.857</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.393</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1.679</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.929</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.179</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.179</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.536</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.464</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.107</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.429</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.964</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.819</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.821</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>00:02</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>5.524</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.624</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.183</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.148</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#13 L. COSTA (Per Game)</t>
+          <t>#15 J. SASTRE (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.269</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.269</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -6156,350 +6156,350 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>00:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>2.251</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.008</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#15 J. SASTRE (Per Game)</t>
+          <t>#16 D. BORDÓN (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C39" t="n">
-        <v>2.545</v>
+        <v>0.364</v>
       </c>
       <c r="D39" t="n">
-        <v>0.318</v>
+        <v>0.182</v>
       </c>
       <c r="E39" t="n">
-        <v>0.864</v>
+        <v>0.545</v>
       </c>
       <c r="F39" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1.273</v>
+        <v>0.182</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>0.273</v>
       </c>
-      <c r="I39" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AA39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1.091</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.182</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="T39" t="n">
-        <v>74</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.611</v>
       </c>
       <c r="AB39" t="n">
         <v>0.091</v>
       </c>
       <c r="AC39" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0.273</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.136</v>
-      </c>
       <c r="AG39" t="n">
         <v>0</v>
       </c>
       <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
         <v>0.182</v>
       </c>
-      <c r="AI39" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AJ39" t="n">
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="AO39" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK39" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AO39" t="n">
-        <v>2.524</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.009</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AV39" t="n">
-        <v>0.092</v>
+        <v>0.241</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.035</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#16 D. BORDÓN (Per Game)</t>
+          <t>#19 G. SHERMADINI (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C40" t="n">
-        <v>0.25</v>
+        <v>13.267</v>
       </c>
       <c r="D40" t="n">
-        <v>0.125</v>
+        <v>4.733</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>4.533</v>
       </c>
       <c r="J40" t="n">
-        <v>0.125</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>3.567</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="M40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.933</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="T40" t="n">
+        <v>555</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.033</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.567</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>9.132999999999999</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.375</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
       <c r="AH40" t="n">
         <v>0</v>
       </c>
@@ -6513,1476 +6513,1476 @@
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>02:11</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>0.875</v>
+        <v>9.661</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.2</v>
+        <v>0.706</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.2</v>
+        <v>0.763</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.286</v>
+        <v>1.373</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.286</v>
+        <v>0.1</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.5</v>
+        <v>0.966</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.198</v>
+        <v>0.219</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.004</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#19 G. SHERMADINI (Per Game)</t>
+          <t>#21 T. ABROMAITIS (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C41" t="n">
-        <v>13.808</v>
+        <v>5.812</v>
       </c>
       <c r="D41" t="n">
-        <v>4.923</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>6.885</v>
+        <v>1.656</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2.344</v>
       </c>
       <c r="H41" t="n">
-        <v>3.962</v>
+        <v>1.312</v>
       </c>
       <c r="I41" t="n">
-        <v>4.808</v>
+        <v>1.562</v>
       </c>
       <c r="J41" t="n">
-        <v>0.962</v>
+        <v>0.625</v>
       </c>
       <c r="K41" t="n">
-        <v>3.654</v>
+        <v>2.312</v>
       </c>
       <c r="L41" t="n">
-        <v>1.346</v>
+        <v>0.625</v>
       </c>
       <c r="M41" t="n">
-        <v>0.154</v>
+        <v>0.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0.885</v>
+        <v>0.406</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.077</v>
+        <v>0.344</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.077</v>
+        <v>0.344</v>
       </c>
       <c r="R41" t="n">
-        <v>1.962</v>
+        <v>1.906</v>
       </c>
       <c r="S41" t="n">
-        <v>4.308</v>
+        <v>1.469</v>
       </c>
       <c r="T41" t="n">
-        <v>501</v>
+        <v>226</v>
       </c>
       <c r="U41" t="n">
-        <v>1.462</v>
+        <v>0.594</v>
       </c>
       <c r="V41" t="n">
-        <v>2.192</v>
+        <v>0.75</v>
       </c>
       <c r="W41" t="n">
-        <v>0.154</v>
+        <v>0.25</v>
       </c>
       <c r="X41" t="n">
-        <v>0.154</v>
+        <v>0.219</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.846</v>
+        <v>1.938</v>
       </c>
       <c r="Z41" t="n">
-        <v>9.5</v>
+        <v>2.375</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.826</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.962</v>
+        <v>0.188</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.923</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.077</v>
+        <v>0.125</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.269</v>
+        <v>0.281</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.286</v>
+        <v>0.444</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.419</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>10.077</v>
+        <v>5.031</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.715</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.767</v>
+        <v>0.62</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.37</v>
+        <v>1.155</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.107</v>
+        <v>0.068</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.575</v>
+        <v>0.328</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.893</v>
+        <v>1.818</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.226</v>
+        <v>0.143</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.08</v>
+        <v>0.047</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.204</v>
+        <v>0.168</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.039</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#21 T. ABROMAITIS (Per Game)</t>
+          <t>#24 M. SANGARE (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>4.964</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.607</v>
+        <v>0.5</v>
       </c>
       <c r="E42" t="n">
-        <v>1.321</v>
+        <v>0.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.286</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.179</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2.214</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
         <v>0.5</v>
       </c>
-      <c r="M42" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="T42" t="n">
-        <v>169</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.607</v>
-      </c>
       <c r="Z42" t="n">
-        <v>2.071</v>
+        <v>0.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.776</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>00:51</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP42" t="n">
         <v>1</v>
       </c>
-      <c r="AJ42" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
-        <v>4.557</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.525</v>
-      </c>
       <c r="AQ42" t="n">
-        <v>0.586</v>
+        <v>1</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.089</v>
+        <v>2</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.327</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.136</v>
+        <v>0.291</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.164</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#24 M. SANGARE (Per Game)</t>
+          <t>#31 R. GIEDRAITIS (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>7.138</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>1.862</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1.241</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>3.103</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1.483</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1.517</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2.103</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.828</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>0.414</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.138</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.276</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>246</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.897</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.034</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.414</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="Y43" t="n">
-        <v>1</v>
+        <v>2.31</v>
       </c>
       <c r="Z43" t="n">
-        <v>1</v>
+        <v>2.759</v>
       </c>
       <c r="AA43" t="n">
-        <v>1</v>
+        <v>0.837</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1.414</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>0.488</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.327</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>01:42</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>1</v>
+        <v>6.15</v>
       </c>
       <c r="AP43" t="n">
-        <v>1</v>
+        <v>0.569</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1</v>
+        <v>0.634</v>
       </c>
       <c r="AR43" t="n">
-        <v>2</v>
+        <v>1.161</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>0.299</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.292</v>
+        <v>0.168</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#31 R. GIEDRAITIS (Per Game)</t>
+          <t>#33 H. ALDERETE (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C44" t="n">
-        <v>7.071</v>
+        <v>0.6</v>
       </c>
       <c r="D44" t="n">
-        <v>0.964</v>
+        <v>0.12</v>
       </c>
       <c r="E44" t="n">
-        <v>1.857</v>
+        <v>0.12</v>
       </c>
       <c r="F44" t="n">
-        <v>1.214</v>
+        <v>0.12</v>
       </c>
       <c r="G44" t="n">
-        <v>3.071</v>
+        <v>0.32</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1.536</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T44" t="n">
+        <v>15</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>0.5</v>
       </c>
-      <c r="K44" t="n">
-        <v>2.179</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.821</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.107</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="AK44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>04:19</t>
+        </is>
+      </c>
+      <c r="AO44" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="AR44" t="n">
         <v>1.25</v>
       </c>
-      <c r="T44" t="n">
-        <v>238</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.321</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.786</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.714</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>6.104</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.158</v>
-      </c>
       <c r="AS44" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.166</v>
+        <v>0.055</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.049</v>
+        <v>0.06</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.147</v>
+        <v>0.128</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#33 H. ALDERETE (Per Game)</t>
+          <t>#35 F. GUERRA (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C45" t="n">
-        <v>0.476</v>
+        <v>6.438</v>
       </c>
       <c r="D45" t="n">
-        <v>0.095</v>
+        <v>2.344</v>
       </c>
       <c r="E45" t="n">
-        <v>0.095</v>
+        <v>3.75</v>
       </c>
       <c r="F45" t="n">
-        <v>0.095</v>
+        <v>0.031</v>
       </c>
       <c r="G45" t="n">
-        <v>0.238</v>
+        <v>0.188</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1.656</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2.531</v>
       </c>
       <c r="J45" t="n">
-        <v>0.19</v>
+        <v>1.688</v>
       </c>
       <c r="K45" t="n">
-        <v>0.19</v>
+        <v>2.438</v>
       </c>
       <c r="L45" t="n">
-        <v>0.19</v>
+        <v>1.031</v>
       </c>
       <c r="M45" t="n">
-        <v>0.048</v>
+        <v>0.469</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.048</v>
+        <v>1.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.048</v>
+        <v>1.25</v>
       </c>
       <c r="R45" t="n">
-        <v>0.571</v>
+        <v>2.156</v>
       </c>
       <c r="S45" t="n">
-        <v>0.143</v>
+        <v>2.656</v>
       </c>
       <c r="T45" t="n">
-        <v>10</v>
+        <v>297</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="V45" t="n">
-        <v>0.238</v>
+        <v>0.531</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.048</v>
+        <v>3.406</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.048</v>
+        <v>4.875</v>
       </c>
       <c r="AA45" t="n">
-        <v>1</v>
+        <v>0.699</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.048</v>
+        <v>0.531</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.048</v>
+        <v>1.188</v>
       </c>
       <c r="AD45" t="n">
-        <v>1</v>
+        <v>0.447</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.048</v>
+        <v>0.031</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.143</v>
+        <v>0.188</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>03:13</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>0.381</v>
+        <v>6.301</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.714</v>
+        <v>0.607</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.714</v>
+        <v>0.637</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.25</v>
+        <v>1.022</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.125</v>
+        <v>0.198</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="AU45" t="n">
-        <v>4</v>
+        <v>1.35</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.059</v>
+        <v>0.188</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.078</v>
+        <v>0.081</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.073</v>
+        <v>0.186</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.006</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#35 F. GUERRA (Per Game)</t>
+          <t>#42 A. DOORNEKAMP (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C46" t="n">
-        <v>6.25</v>
+        <v>6.8</v>
       </c>
       <c r="D46" t="n">
-        <v>2.25</v>
+        <v>0.467</v>
       </c>
       <c r="E46" t="n">
-        <v>3.607</v>
+        <v>0.667</v>
       </c>
       <c r="F46" t="n">
-        <v>0.036</v>
+        <v>1.767</v>
       </c>
       <c r="G46" t="n">
-        <v>0.214</v>
+        <v>4.267</v>
       </c>
       <c r="H46" t="n">
-        <v>1.643</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>0.767</v>
       </c>
       <c r="J46" t="n">
-        <v>1.786</v>
+        <v>1.067</v>
       </c>
       <c r="K46" t="n">
-        <v>2.464</v>
+        <v>2.633</v>
       </c>
       <c r="L46" t="n">
-        <v>1.036</v>
+        <v>0.6</v>
       </c>
       <c r="M46" t="n">
-        <v>0.464</v>
+        <v>0.967</v>
       </c>
       <c r="N46" t="n">
-        <v>0.464</v>
+        <v>0.167</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.214</v>
+        <v>0.467</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.214</v>
+        <v>0.467</v>
       </c>
       <c r="R46" t="n">
-        <v>2.179</v>
+        <v>2.767</v>
       </c>
       <c r="S46" t="n">
-        <v>2.679</v>
+        <v>1.567</v>
       </c>
       <c r="T46" t="n">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="U46" t="n">
-        <v>0.179</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="V46" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AD46" t="n">
         <v>0.5</v>
       </c>
-      <c r="W46" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>3.321</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>4.821</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.107</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0.452</v>
-      </c>
       <c r="AE46" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.233</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.179</v>
+        <v>0.367</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.4</v>
+        <v>0.636</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>1.633</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.036</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.214</v>
+        <v>2.633</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.167</v>
+        <v>0.354</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>6.136</v>
+        <v>5.737</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.603</v>
+        <v>0.632</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.635</v>
+        <v>0.645</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.019</v>
+        <v>1.185</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.198</v>
+        <v>0.081</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.43</v>
+        <v>0.115</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.471</v>
+        <v>2.286</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.186</v>
+        <v>0.124</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.083</v>
+        <v>0.034</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.185</v>
+        <v>0.145</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.065</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#42 A. DOORNEKAMP (Per Game)</t>
+          <t>#88 P. MILLS (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>7.071</v>
+        <v>18.667</v>
       </c>
       <c r="D47" t="n">
-        <v>0.393</v>
+        <v>2.333</v>
       </c>
       <c r="E47" t="n">
-        <v>0.607</v>
+        <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>1.893</v>
+        <v>3.667</v>
       </c>
       <c r="G47" t="n">
-        <v>4.429</v>
+        <v>7.778</v>
       </c>
       <c r="H47" t="n">
-        <v>0.607</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.821</v>
+        <v>3.667</v>
       </c>
       <c r="J47" t="n">
-        <v>1.036</v>
+        <v>1.667</v>
       </c>
       <c r="K47" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.607</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.893</v>
+        <v>0.778</v>
       </c>
       <c r="N47" t="n">
-        <v>0.179</v>
+        <v>0.444</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.5</v>
+        <v>1.333</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.5</v>
+        <v>1.333</v>
       </c>
       <c r="R47" t="n">
-        <v>2.786</v>
+        <v>1.556</v>
       </c>
       <c r="S47" t="n">
-        <v>1.607</v>
+        <v>4.111</v>
       </c>
       <c r="T47" t="n">
-        <v>214</v>
+        <v>147</v>
       </c>
       <c r="U47" t="n">
-        <v>0.607</v>
+        <v>1.889</v>
       </c>
       <c r="V47" t="n">
-        <v>0.821</v>
+        <v>1.889</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.556</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.821</v>
+        <v>4.111</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.071</v>
+        <v>4.889</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.767</v>
+        <v>0.841</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.036</v>
+        <v>0.778</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.179</v>
+        <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.321</v>
+        <v>3</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.893</v>
+        <v>0.667</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.679</v>
+        <v>1.444</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.532</v>
+        <v>0.462</v>
       </c>
       <c r="AK47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.75</v>
+        <v>6.333</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.364</v>
+        <v>0.474</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>5.897</v>
+        <v>15.724</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.642</v>
+        <v>0.613</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.655</v>
+        <v>0.649</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.199</v>
+        <v>1.187</v>
       </c>
       <c r="AS47" t="n">
         <v>0.08500000000000001</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.121</v>
+        <v>0.235</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.071</v>
+        <v>1.25</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.127</v>
+        <v>0.347</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.134</v>
+        <v>0.056</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.038</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#88 P. MILLS (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>1.406</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.906</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.2</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>0.094</v>
       </c>
       <c r="S48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.913</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.469</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>14.384</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.698</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.279</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.293</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.371</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
         <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>89.03100000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>19.375</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>33.688</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>10.781</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>27.188</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>17.938</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>21.719</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>17.812</v>
       </c>
       <c r="K49" t="n">
-        <v>1.464</v>
+        <v>22.344</v>
       </c>
       <c r="L49" t="n">
-        <v>0.821</v>
+        <v>7.688</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>6.406</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.219</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>10.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>9.811999999999999</v>
       </c>
       <c r="R49" t="n">
-        <v>0.107</v>
+        <v>20.844</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>22.812</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3335</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>9.156000000000001</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.438</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>28.719</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>36.344</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>3.812</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>8.781000000000001</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.434</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>4.781</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>10.281</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>3.344</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>7.438</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>7.438</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>19.75</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>81.181</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.097</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.657</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7991,477 +7991,159 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>86.15600000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>21.219</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>37.781</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>8.875</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>23.531</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>17.094</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>21.969</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>15.812</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>23.125</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>6.219</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.406</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>11.906</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>23.031</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>20.656</v>
       </c>
       <c r="T50" t="n">
-        <v>33</v>
+        <v>3033</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>11.125</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>5.844</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.281</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>30.375</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>39.938</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.761</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>4.438</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>10.906</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>0.407</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>8.906000000000001</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>5.312</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.471</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>18.219</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>1</v>
+        <v>82.88500000000001</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.039</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.279</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.328</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>28</v>
-      </c>
-      <c r="C51" t="n">
-        <v>88.643</v>
-      </c>
-      <c r="D51" t="n">
-        <v>18.893</v>
-      </c>
-      <c r="E51" t="n">
-        <v>32.714</v>
-      </c>
-      <c r="F51" t="n">
-        <v>10.786</v>
-      </c>
-      <c r="G51" t="n">
-        <v>27.143</v>
-      </c>
-      <c r="H51" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I51" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="J51" t="n">
-        <v>18.071</v>
-      </c>
-      <c r="K51" t="n">
-        <v>22.429</v>
-      </c>
-      <c r="L51" t="n">
-        <v>7.714</v>
-      </c>
-      <c r="M51" t="n">
-        <v>6.214</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.429</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>10.929</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>9.929</v>
-      </c>
-      <c r="R51" t="n">
-        <v>21</v>
-      </c>
-      <c r="S51" t="n">
-        <v>23.214</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2936</v>
-      </c>
-      <c r="U51" t="n">
-        <v>9.036</v>
-      </c>
-      <c r="V51" t="n">
-        <v>10</v>
-      </c>
-      <c r="W51" t="n">
-        <v>2.321</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.679</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>29.107</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>36.857</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>3.607</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>4.679</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>9.856999999999999</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>3.536</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>7.536</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>19.607</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>80.57599999999999</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>1.654</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>28</v>
-      </c>
-      <c r="C52" t="n">
-        <v>84.393</v>
-      </c>
-      <c r="D52" t="n">
-        <v>20.821</v>
-      </c>
-      <c r="E52" t="n">
-        <v>37.679</v>
-      </c>
-      <c r="F52" t="n">
-        <v>8.606999999999999</v>
-      </c>
-      <c r="G52" t="n">
-        <v>23.786</v>
-      </c>
-      <c r="H52" t="n">
-        <v>16.929</v>
-      </c>
-      <c r="I52" t="n">
-        <v>21.893</v>
-      </c>
-      <c r="J52" t="n">
-        <v>15.929</v>
-      </c>
-      <c r="K52" t="n">
-        <v>22.571</v>
-      </c>
-      <c r="L52" t="n">
-        <v>9.964</v>
-      </c>
-      <c r="M52" t="n">
-        <v>6.393</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.607</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>11.929</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>10.929</v>
-      </c>
-      <c r="R52" t="n">
-        <v>23.464</v>
-      </c>
-      <c r="S52" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2582</v>
-      </c>
-      <c r="U52" t="n">
-        <v>11.571</v>
-      </c>
-      <c r="V52" t="n">
-        <v>9.714</v>
-      </c>
-      <c r="W52" t="n">
-        <v>5.464</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>29.964</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>39.964</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>4.429</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.214</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>3.357</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>8.393000000000001</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.536</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>5.464</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>6.071</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>18.321</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>83.026</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>1.335</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AY52" t="n">
         <v>0</v>
       </c>
     </row>
